--- a/outpatient_specialty_categories_hes_omop.V.0.xlsx
+++ b/outpatient_specialty_categories_hes_omop.V.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms0952_ox_ac_uk/Documents/OMOP_Validation study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{47E17E6E-9134-4AFE-A380-2F9C1FFD29AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98BE80E3-DD56-4C93-B934-B21CC6F71219}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{47E17E6E-9134-4AFE-A380-2F9C1FFD29AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDE7EEB3-EA14-4BDC-BCF4-E2E2A544CF0C}"/>
   <bookViews>
-    <workbookView xWindow="29940" yWindow="1740" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined_list" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="209">
   <si>
     <t>concept_name</t>
   </si>
@@ -647,6 +647,30 @@
   </si>
   <si>
     <t>Pathology</t>
+  </si>
+  <si>
+    <t>Intermediate care</t>
+  </si>
+  <si>
+    <t>Breast surgery</t>
+  </si>
+  <si>
+    <t>Restorative dentistry</t>
+  </si>
+  <si>
+    <t>Hepatobiliary &amp; pancreatic surgery</t>
+  </si>
+  <si>
+    <t>Cardiothoracic transplantation</t>
+  </si>
+  <si>
+    <t>Transplantation surgery</t>
+  </si>
+  <si>
+    <t>Haemophilia</t>
+  </si>
+  <si>
+    <t>Bone and marrow transplantation</t>
   </si>
 </sst>
 </file>
@@ -1019,14 +1043,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D91692-E2A8-4FFF-B60D-B8C034084F43}">
   <dimension ref="A1:C162"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="92.140625" customWidth="1"/>
-    <col min="2" max="2" width="44.140625" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="92.109375" customWidth="1"/>
+    <col min="2" max="2" width="44.109375" customWidth="1"/>
+    <col min="3" max="3" width="44.109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>192</v>
       </c>
@@ -1037,7 +1061,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>144</v>
       </c>
@@ -1048,7 +1072,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1059,7 +1083,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1070,7 +1094,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1081,7 +1105,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>135</v>
       </c>
@@ -1092,7 +1116,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1103,7 +1127,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -1114,7 +1138,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>165</v>
       </c>
@@ -1125,7 +1149,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>78</v>
       </c>
@@ -1136,7 +1160,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -1147,7 +1171,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>103</v>
       </c>
@@ -1158,7 +1182,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -1169,7 +1193,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -1180,7 +1204,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -1191,7 +1215,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -1202,7 +1226,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1213,7 +1237,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>141</v>
       </c>
@@ -1224,7 +1248,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1235,7 +1259,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>110</v>
       </c>
@@ -1246,7 +1270,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>111</v>
       </c>
@@ -1257,7 +1281,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>112</v>
       </c>
@@ -1268,7 +1292,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1279,7 +1303,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -1290,7 +1314,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -1301,7 +1325,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -1312,7 +1336,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1323,7 +1347,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -1334,7 +1358,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1345,7 +1369,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -1356,7 +1380,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -1367,7 +1391,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -1378,7 +1402,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>166</v>
       </c>
@@ -1389,7 +1413,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -1400,7 +1424,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>41</v>
       </c>
@@ -1411,7 +1435,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>129</v>
       </c>
@@ -1422,7 +1446,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -1433,7 +1457,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -1444,7 +1468,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>83</v>
       </c>
@@ -1455,7 +1479,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>127</v>
       </c>
@@ -1466,7 +1490,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>130</v>
       </c>
@@ -1477,7 +1501,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>131</v>
       </c>
@@ -1488,7 +1512,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>168</v>
       </c>
@@ -1499,7 +1523,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>107</v>
       </c>
@@ -1510,7 +1534,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>108</v>
       </c>
@@ -1521,7 +1545,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -1532,7 +1556,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>132</v>
       </c>
@@ -1543,7 +1567,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>42</v>
       </c>
@@ -1554,7 +1578,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>43</v>
       </c>
@@ -1565,7 +1589,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>47</v>
       </c>
@@ -1576,7 +1600,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -1587,7 +1611,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>139</v>
       </c>
@@ -1598,7 +1622,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -1609,7 +1633,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>126</v>
       </c>
@@ -1620,7 +1644,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>46</v>
       </c>
@@ -1631,7 +1655,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1642,7 +1666,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -1653,7 +1677,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>70</v>
       </c>
@@ -1664,7 +1688,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>81</v>
       </c>
@@ -1675,7 +1699,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>84</v>
       </c>
@@ -1686,7 +1710,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>48</v>
       </c>
@@ -1697,7 +1721,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>59</v>
       </c>
@@ -1708,7 +1732,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>31</v>
       </c>
@@ -1719,7 +1743,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>32</v>
       </c>
@@ -1730,7 +1754,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>137</v>
       </c>
@@ -1741,7 +1765,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>157</v>
       </c>
@@ -1752,7 +1776,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>140</v>
       </c>
@@ -1763,7 +1787,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>20</v>
       </c>
@@ -1774,7 +1798,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -1785,7 +1809,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>2</v>
       </c>
@@ -1796,7 +1820,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>26</v>
       </c>
@@ -1807,7 +1831,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -1818,7 +1842,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>158</v>
       </c>
@@ -1829,7 +1853,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -1840,7 +1864,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>22</v>
       </c>
@@ -1851,7 +1875,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -1862,7 +1886,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>159</v>
       </c>
@@ -1873,7 +1897,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>57</v>
       </c>
@@ -1884,7 +1908,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -1895,7 +1919,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>145</v>
       </c>
@@ -1906,7 +1930,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>52</v>
       </c>
@@ -1917,7 +1941,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>61</v>
       </c>
@@ -1928,7 +1952,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>60</v>
       </c>
@@ -1939,7 +1963,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>120</v>
       </c>
@@ -1950,7 +1974,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>28</v>
       </c>
@@ -1961,7 +1985,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>72</v>
       </c>
@@ -1972,7 +1996,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>113</v>
       </c>
@@ -1983,7 +2007,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -1994,7 +2018,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>75</v>
       </c>
@@ -2005,7 +2029,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>76</v>
       </c>
@@ -2016,7 +2040,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>55</v>
       </c>
@@ -2027,7 +2051,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>56</v>
       </c>
@@ -2038,7 +2062,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>54</v>
       </c>
@@ -2049,7 +2073,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>151</v>
       </c>
@@ -2060,7 +2084,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>77</v>
       </c>
@@ -2071,7 +2095,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>149</v>
       </c>
@@ -2082,7 +2106,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>29</v>
       </c>
@@ -2093,7 +2117,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>93</v>
       </c>
@@ -2104,7 +2128,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>68</v>
       </c>
@@ -2115,7 +2139,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>92</v>
       </c>
@@ -2126,7 +2150,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>30</v>
       </c>
@@ -2137,7 +2161,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>136</v>
       </c>
@@ -2148,7 +2172,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>27</v>
       </c>
@@ -2159,7 +2183,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>53</v>
       </c>
@@ -2170,7 +2194,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -2181,7 +2205,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>87</v>
       </c>
@@ -2192,7 +2216,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>88</v>
       </c>
@@ -2203,7 +2227,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>142</v>
       </c>
@@ -2214,7 +2238,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>147</v>
       </c>
@@ -2225,7 +2249,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>89</v>
       </c>
@@ -2236,7 +2260,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>90</v>
       </c>
@@ -2247,7 +2271,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>36</v>
       </c>
@@ -2258,7 +2282,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>152</v>
       </c>
@@ -2269,7 +2293,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>50</v>
       </c>
@@ -2280,7 +2304,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>154</v>
       </c>
@@ -2291,7 +2315,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>19</v>
       </c>
@@ -2302,7 +2326,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>33</v>
       </c>
@@ -2313,7 +2337,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>155</v>
       </c>
@@ -2324,7 +2348,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>80</v>
       </c>
@@ -2335,7 +2359,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>65</v>
       </c>
@@ -2346,7 +2370,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>156</v>
       </c>
@@ -2357,7 +2381,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>79</v>
       </c>
@@ -2368,7 +2392,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>66</v>
       </c>
@@ -2379,7 +2403,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>101</v>
       </c>
@@ -2390,7 +2414,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>63</v>
       </c>
@@ -2401,7 +2425,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>74</v>
       </c>
@@ -2412,7 +2436,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>44</v>
       </c>
@@ -2423,7 +2447,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>102</v>
       </c>
@@ -2434,7 +2458,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>71</v>
       </c>
@@ -2445,7 +2469,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>146</v>
       </c>
@@ -2456,7 +2480,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>99</v>
       </c>
@@ -2467,7 +2491,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>105</v>
       </c>
@@ -2478,7 +2502,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>104</v>
       </c>
@@ -2489,7 +2513,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>106</v>
       </c>
@@ -2500,7 +2524,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>109</v>
       </c>
@@ -2511,7 +2535,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>9</v>
       </c>
@@ -2522,7 +2546,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -2533,7 +2557,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>34</v>
       </c>
@@ -2544,7 +2568,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>51</v>
       </c>
@@ -2555,7 +2579,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>58</v>
       </c>
@@ -2566,7 +2590,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>67</v>
       </c>
@@ -2577,7 +2601,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>73</v>
       </c>
@@ -2588,7 +2612,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>128</v>
       </c>
@@ -2599,7 +2623,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>118</v>
       </c>
@@ -2610,7 +2634,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>133</v>
       </c>
@@ -2621,7 +2645,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>96</v>
       </c>
@@ -2632,7 +2656,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>95</v>
       </c>
@@ -2643,7 +2667,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>114</v>
       </c>
@@ -2654,7 +2678,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>116</v>
       </c>
@@ -2665,7 +2689,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>121</v>
       </c>
@@ -2676,7 +2700,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>123</v>
       </c>
@@ -2687,7 +2711,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>125</v>
       </c>
@@ -2698,7 +2722,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>122</v>
       </c>
@@ -2709,7 +2733,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>17</v>
       </c>
@@ -2720,7 +2744,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>150</v>
       </c>
@@ -2731,7 +2755,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>160</v>
       </c>
@@ -2742,7 +2766,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>161</v>
       </c>
@@ -2753,7 +2777,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>64</v>
       </c>
@@ -2764,7 +2788,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>163</v>
       </c>
@@ -2775,7 +2799,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -2786,7 +2810,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>164</v>
       </c>
@@ -2797,7 +2821,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>167</v>
       </c>
@@ -2821,14 +2845,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="78.85546875" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="78.88671875" customWidth="1"/>
+    <col min="3" max="3" width="39.109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>199</v>
       </c>
@@ -2839,7 +2863,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>38004465</v>
       </c>
@@ -2850,7 +2874,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>38004490</v>
       </c>
@@ -2861,7 +2885,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>38004463</v>
       </c>
@@ -2872,7 +2896,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>38004675</v>
       </c>
@@ -2883,7 +2907,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>38004491</v>
       </c>
@@ -2894,7 +2918,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>38004451</v>
       </c>
@@ -2905,7 +2929,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>38004478</v>
       </c>
@@ -2916,7 +2940,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>38004446</v>
       </c>
@@ -2927,7 +2951,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>44807945</v>
       </c>
@@ -2938,7 +2962,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>38004452</v>
       </c>
@@ -2949,7 +2973,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>38004492</v>
       </c>
@@ -2960,7 +2984,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>38004472</v>
       </c>
@@ -2971,7 +2995,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>38004449</v>
       </c>
@@ -2982,7 +3006,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>38003902</v>
       </c>
@@ -2993,7 +3017,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>38004447</v>
       </c>
@@ -3004,7 +3028,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>38004489</v>
       </c>
@@ -3015,7 +3039,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>38004455</v>
       </c>
@@ -3026,18 +3050,18 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>44777808</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>201</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>38004458</v>
       </c>
@@ -3048,7 +3072,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>38004501</v>
       </c>
@@ -3059,7 +3083,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>38004486</v>
       </c>
@@ -3070,7 +3094,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>38004470</v>
       </c>
@@ -3081,7 +3105,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>38004468</v>
       </c>
@@ -3092,7 +3116,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>44777714</v>
       </c>
@@ -3103,7 +3127,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>38004474</v>
       </c>
@@ -3114,7 +3138,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>38004494</v>
       </c>
@@ -3125,7 +3149,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>38004467</v>
       </c>
@@ -3136,7 +3160,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>38004469</v>
       </c>
@@ -3147,7 +3171,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>38004479</v>
       </c>
@@ -3158,7 +3182,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>44777680</v>
       </c>
@@ -3169,18 +3193,18 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>44777667</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>38004471</v>
       </c>
@@ -3191,7 +3215,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>38004493</v>
       </c>
@@ -3202,7 +3226,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>38004464</v>
       </c>
@@ -3213,7 +3237,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>38004459</v>
       </c>
@@ -3224,7 +3248,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>38004496</v>
       </c>
@@ -3235,7 +3259,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>38004694</v>
       </c>
@@ -3246,7 +3270,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38004485</v>
       </c>
@@ -3257,7 +3281,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38004509</v>
       </c>
@@ -3268,7 +3292,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>38004489</v>
       </c>
@@ -3279,7 +3303,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>38004504</v>
       </c>
@@ -3290,7 +3314,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>38004684</v>
       </c>
@@ -3301,7 +3325,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>38004450</v>
       </c>
@@ -3312,7 +3336,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44777712</v>
       </c>
@@ -3323,7 +3347,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45757046</v>
       </c>
@@ -3334,7 +3358,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>38004510</v>
       </c>
@@ -3345,7 +3369,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4235390</v>
       </c>
@@ -3356,18 +3380,18 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>44777671</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>44777734</v>
       </c>
@@ -3378,7 +3402,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>38004507</v>
       </c>
@@ -3389,7 +3413,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>45756763</v>
       </c>
@@ -3400,7 +3424,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>44808148</v>
       </c>
@@ -3411,7 +3435,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>38004462</v>
       </c>
@@ -3422,7 +3446,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>38004122</v>
       </c>
@@ -3433,7 +3457,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>38004513</v>
       </c>
@@ -3444,7 +3468,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>38004511</v>
       </c>
@@ -3455,7 +3479,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>38003876</v>
       </c>
@@ -3466,7 +3490,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>44811325</v>
       </c>
@@ -3477,7 +3501,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>44777669</v>
       </c>
@@ -3488,7 +3512,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>903277</v>
       </c>
@@ -3499,7 +3523,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>38004463</v>
       </c>
@@ -3510,7 +3534,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>45756825</v>
       </c>
@@ -3521,7 +3545,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>37117769</v>
       </c>
@@ -3532,7 +3556,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>45756796</v>
       </c>
@@ -3543,7 +3567,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>38004493</v>
       </c>
@@ -3554,7 +3578,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>38004469</v>
       </c>
@@ -3565,7 +3589,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>38003830</v>
       </c>
@@ -3576,7 +3600,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>44814160</v>
       </c>
@@ -3587,18 +3611,18 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>44777668</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>204</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>38004497</v>
       </c>
@@ -3609,7 +3633,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>38004484</v>
       </c>
@@ -3620,18 +3644,18 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>44777676</v>
       </c>
       <c r="B73" t="s">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>38004476</v>
       </c>
@@ -3642,7 +3666,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>38004481</v>
       </c>
@@ -3653,7 +3677,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>45756830</v>
       </c>
@@ -3664,7 +3688,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>44777674</v>
       </c>
@@ -3675,7 +3699,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>38004448</v>
       </c>
@@ -3686,7 +3710,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>38004030</v>
       </c>
@@ -3697,18 +3721,18 @@
         <v>174</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>44777666</v>
       </c>
       <c r="B80" t="s">
-        <v>116</v>
+        <v>206</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>38004473</v>
       </c>
@@ -3719,7 +3743,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>45757046</v>
       </c>
@@ -3730,7 +3754,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>44777719</v>
       </c>
@@ -3741,7 +3765,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>44777753</v>
       </c>
@@ -3752,7 +3776,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>32580</v>
       </c>
@@ -3763,7 +3787,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>38004025</v>
       </c>
@@ -3774,18 +3798,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>44777801</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>207</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>44777755</v>
       </c>
@@ -3796,7 +3820,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>38004063</v>
       </c>
@@ -3807,7 +3831,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>4214701</v>
       </c>
@@ -3818,7 +3842,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>38004098</v>
       </c>
@@ -3829,7 +3853,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>45756760</v>
       </c>
@@ -3840,7 +3864,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>44777684</v>
       </c>
@@ -3851,7 +3875,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>38004500</v>
       </c>
@@ -3862,7 +3886,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>45756748</v>
       </c>
@@ -3873,7 +3897,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>38004685</v>
       </c>
@@ -3884,7 +3908,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>44777741</v>
       </c>
@@ -3895,7 +3919,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>38003905</v>
       </c>
@@ -3906,7 +3930,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>38004063</v>
       </c>
@@ -3917,7 +3941,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>903263</v>
       </c>
@@ -3928,7 +3952,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>45756756</v>
       </c>
@@ -3939,7 +3963,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>44777673</v>
       </c>
@@ -3950,7 +3974,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>44777687</v>
       </c>
@@ -3961,7 +3985,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>38004477</v>
       </c>
@@ -3972,18 +3996,18 @@
         <v>89</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>44777800</v>
       </c>
       <c r="B105" t="s">
-        <v>8</v>
+        <v>208</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>45756814</v>
       </c>
@@ -4003,14 +4027,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB853A77-C2E6-4F72-8593-B5786C9259A0}">
   <dimension ref="A1:C90"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="147" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>195</v>
       </c>
@@ -4021,7 +4045,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>326</v>
       </c>
@@ -4032,7 +4056,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>710</v>
       </c>
@@ -4043,7 +4067,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>317</v>
       </c>
@@ -4054,7 +4078,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>960</v>
       </c>
@@ -4065,7 +4089,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>190</v>
       </c>
@@ -4076,7 +4100,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>310</v>
       </c>
@@ -4087,7 +4111,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>200</v>
       </c>
@@ -4098,7 +4122,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>821</v>
       </c>
@@ -4109,7 +4133,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>320</v>
       </c>
@@ -4120,7 +4144,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>170</v>
       </c>
@@ -4131,7 +4155,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>822</v>
       </c>
@@ -4142,7 +4166,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>711</v>
       </c>
@@ -4153,7 +4177,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>312</v>
       </c>
@@ -4164,7 +4188,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>311</v>
       </c>
@@ -4175,7 +4199,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>303</v>
       </c>
@@ -4186,7 +4210,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>313</v>
       </c>
@@ -4197,7 +4221,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>401</v>
       </c>
@@ -4208,7 +4232,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>800</v>
       </c>
@@ -4219,7 +4243,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>305</v>
       </c>
@@ -4230,7 +4254,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>304</v>
       </c>
@@ -4241,7 +4265,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>902</v>
       </c>
@@ -4252,7 +4276,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>900</v>
       </c>
@@ -4263,7 +4287,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>504</v>
       </c>
@@ -4274,7 +4298,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>450</v>
       </c>
@@ -4285,7 +4309,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>330</v>
       </c>
@@ -4296,7 +4320,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>120</v>
       </c>
@@ -4307,7 +4331,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>180</v>
       </c>
@@ -4318,7 +4342,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>302</v>
       </c>
@@ -4329,7 +4353,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>146</v>
       </c>
@@ -4340,7 +4364,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>712</v>
       </c>
@@ -4351,7 +4375,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>301</v>
       </c>
@@ -4362,7 +4386,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>601</v>
       </c>
@@ -4373,7 +4397,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>300</v>
       </c>
@@ -4384,7 +4408,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>600</v>
       </c>
@@ -4395,7 +4419,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>820</v>
       </c>
@@ -4406,7 +4430,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>100</v>
       </c>
@@ -4417,7 +4441,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>360</v>
       </c>
@@ -4428,7 +4452,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>430</v>
       </c>
@@ -4439,7 +4463,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>502</v>
       </c>
@@ -4450,7 +4474,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>823</v>
       </c>
@@ -4461,7 +4485,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>824</v>
       </c>
@@ -4472,7 +4496,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>830</v>
       </c>
@@ -4483,7 +4507,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>350</v>
       </c>
@@ -4494,7 +4518,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>192</v>
       </c>
@@ -4505,7 +4529,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>700</v>
       </c>
@@ -4516,7 +4540,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>833</v>
       </c>
@@ -4527,7 +4551,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>831</v>
       </c>
@@ -4538,7 +4562,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>370</v>
       </c>
@@ -4549,7 +4573,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>460</v>
       </c>
@@ -4560,7 +4584,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>713</v>
       </c>
@@ -4571,7 +4595,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>834</v>
       </c>
@@ -4582,7 +4606,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>560</v>
       </c>
@@ -4593,7 +4617,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>400</v>
       </c>
@@ -4604,7 +4628,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>150</v>
       </c>
@@ -4615,7 +4639,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>371</v>
       </c>
@@ -4626,7 +4650,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>950</v>
       </c>
@@ -4637,7 +4661,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>501</v>
       </c>
@@ -4648,7 +4672,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>500</v>
       </c>
@@ -4659,7 +4683,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>901</v>
       </c>
@@ -4670,7 +4694,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>715</v>
       </c>
@@ -4681,7 +4705,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>130</v>
       </c>
@@ -4692,7 +4716,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>145</v>
       </c>
@@ -4703,7 +4727,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>140</v>
       </c>
@@ -4714,7 +4738,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>143</v>
       </c>
@@ -4725,7 +4749,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>321</v>
       </c>
@@ -4736,7 +4760,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>142</v>
       </c>
@@ -4747,7 +4771,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>421</v>
       </c>
@@ -4758,7 +4782,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>171</v>
       </c>
@@ -4769,7 +4793,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>420</v>
       </c>
@@ -4780,7 +4804,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>191</v>
       </c>
@@ -4791,7 +4815,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>315</v>
       </c>
@@ -4802,7 +4826,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>147</v>
       </c>
@@ -4813,7 +4837,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>160</v>
       </c>
@@ -4824,7 +4848,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>148</v>
       </c>
@@ -4835,7 +4859,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>904</v>
       </c>
@@ -4846,7 +4870,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>903</v>
       </c>
@@ -4857,7 +4881,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>810</v>
       </c>
@@ -4868,7 +4892,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>314</v>
       </c>
@@ -4879,7 +4903,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>361</v>
       </c>
@@ -4890,7 +4914,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>340</v>
       </c>
@@ -4901,7 +4925,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>141</v>
       </c>
@@ -4912,7 +4936,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>410</v>
       </c>
@@ -4923,7 +4947,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>451</v>
       </c>
@@ -4934,7 +4958,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>325</v>
       </c>
@@ -4945,7 +4969,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>149</v>
       </c>
@@ -4956,7 +4980,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>110</v>
       </c>
@@ -4967,7 +4991,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>352</v>
       </c>
@@ -4978,7 +5002,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>101</v>
       </c>
@@ -4989,7 +5013,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>107</v>
       </c>
@@ -5009,19 +5033,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5DD060A-7075-4B76-983B-AF8A6B081901}">
   <dimension ref="D5:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>198</v>
       </c>
@@ -5032,6 +5056,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1fd57a85-5f09-446c-9d29-22a13ed0863b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="47a2ec26-e196-46c3-886b-68c32d2bf91e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E261632A9079424993A897DC15346D5B" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="250f8431ed4c7e234790b24d3ac7453a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1fd57a85-5f09-446c-9d29-22a13ed0863b" xmlns:ns3="47a2ec26-e196-46c3-886b-68c32d2bf91e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3ff1c57d4084187fab6d1784df49346" ns2:_="" ns3:_="">
     <xsd:import namespace="1fd57a85-5f09-446c-9d29-22a13ed0863b"/>
@@ -5286,34 +5330,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1fd57a85-5f09-446c-9d29-22a13ed0863b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="47a2ec26-e196-46c3-886b-68c32d2bf91e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2BF0036-FD58-4920-8A48-D933218FE52D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9264439-343F-452A-BCEF-70C48E514666}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1fd57a85-5f09-446c-9d29-22a13ed0863b"/>
+    <ds:schemaRef ds:uri="47a2ec26-e196-46c3-886b-68c32d2bf91e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBE7A7A1-DAED-400E-BFF5-BC30C63F3ADE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBE7A7A1-DAED-400E-BFF5-BC30C63F3ADE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9264439-343F-452A-BCEF-70C48E514666}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2BF0036-FD58-4920-8A48-D933218FE52D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1fd57a85-5f09-446c-9d29-22a13ed0863b"/>
+    <ds:schemaRef ds:uri="47a2ec26-e196-46c3-886b-68c32d2bf91e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>